--- a/ig/DM-SIDOBA/ValueSet-jdv-j409-type-adresse-ms.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-jdv-j409-type-adresse-ms.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Type d'adresse postale.</t>
+    <t>Type d'adresse postale tel que "Adresse du domicile", "Adresse de livraison" pour une personne physique.</t>
   </si>
   <si>
     <t>Purpose</t>
